--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484552_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484552_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9754</v>
+        <v>3.4209</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2034</v>
+        <v>3.4507</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.228</v>
+        <v>-0.0298</v>
       </c>
       <c r="G2" t="n">
         <v>2.3623</v>
@@ -610,13 +610,13 @@
         <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.0641</v>
       </c>
       <c r="T2" t="n">
-        <v>0.181</v>
+        <v>0.4284</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6907</v>
+        <v>-0.4925</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8931</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>J. CARRERAS MUNOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8696</v>
+        <v>2.236</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1613</v>
+        <v>3.3864</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7083</v>
+        <v>-1.1504</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4776</v>
+        <v>1.7669</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4941</v>
+        <v>2.4852</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.9717</v>
+        <v>-0.7183</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5669999999999999</v>
+        <v>2.6833</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9997</v>
+        <v>1.9908</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4327</v>
+        <v>0.6925</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0446</v>
+        <v>-0.9164</v>
       </c>
       <c r="N3" t="n">
         <v>0.4944</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5391</v>
+        <v>-1.4109</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5305</v>
+        <v>-0.4576</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2436</v>
+        <v>0.342</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2869</v>
+        <v>-0.7996</v>
       </c>
       <c r="V3" t="n">
-        <v>1.267</v>
+        <v>0.0104</v>
       </c>
       <c r="W3" t="n">
-        <v>1.267</v>
+        <v>1.2774</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4248</v>
+        <v>2.0616</v>
       </c>
       <c r="E4" t="n">
-        <v>0.121</v>
+        <v>0.0799</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3037</v>
+        <v>1.9817</v>
       </c>
       <c r="G4" t="n">
         <v>2.9136</v>
@@ -766,13 +766,13 @@
         <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>0.593</v>
+        <v>0.2298</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2723</v>
+        <v>0.2312</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3207</v>
+        <v>-0.0014</v>
       </c>
       <c r="V4" t="n">
         <v>0.3843</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUNOZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6145</v>
+        <v>1.7839</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9879</v>
+        <v>1.4471</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3734</v>
+        <v>0.3367</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7669</v>
+        <v>-0.4776</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4852</v>
+        <v>1.4941</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7183</v>
+        <v>-1.9717</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6833</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9908</v>
+        <v>0.9997</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6925</v>
+        <v>-0.4327</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9164</v>
+        <v>-1.0446</v>
       </c>
       <c r="N5" t="n">
         <v>0.4944</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4109</v>
+        <v>-1.5391</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0791</v>
+        <v>0.4448</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0565</v>
+        <v>0.5294</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0226</v>
+        <v>-0.0847</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0104</v>
+        <v>1.267</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2774</v>
+        <v>1.267</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2331</v>
+        <v>1.3131</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7033</v>
+        <v>-1.1519</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5298</v>
+        <v>2.465</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5458</v>
+        <v>-0.1146</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0779</v>
+        <v>-0.1213</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4678</v>
+        <v>0.0067</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.3209</v>
+        <v>-1.7232</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1737</v>
+        <v>-1.217</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1472</v>
+        <v>-0.5062</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7751</v>
+        <v>1.6086</v>
       </c>
       <c r="N7" t="n">
         <v>1.0958</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3207</v>
+        <v>0.5128</v>
       </c>
       <c r="P7" t="n">
         <v>0.733</v>
@@ -1000,28 +1000,28 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6823</v>
+        <v>0.0092</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7572</v>
+        <v>0.5713</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3634</v>
+        <v>0.6854</v>
       </c>
       <c r="W7" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9035</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>M. BERENGUER CASCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8398</v>
+        <v>1.1597</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3031</v>
+        <v>0.0941</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1429</v>
+        <v>1.0655</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1146</v>
+        <v>2.0764</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1213</v>
+        <v>-0.1803</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0067</v>
+        <v>2.2568</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7232</v>
+        <v>1.5443</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.217</v>
+        <v>-0.6167</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5062</v>
+        <v>2.161</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6086</v>
+        <v>0.5321</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0958</v>
+        <v>0.4364</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5128</v>
+        <v>0.0958</v>
       </c>
       <c r="P8" t="n">
         <v>0.733</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>2.5656</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.464</v>
+        <v>0.1883</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4201</v>
+        <v>0.3824</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8841</v>
+        <v>-0.194</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6854</v>
+        <v>-1.8381</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6854</v>
+        <v>-1.8381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BERENGUER CASCO</t>
+          <t>A. ORTEGA IBAÑEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7943</v>
+        <v>0.6502</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3456</v>
+        <v>0.6502</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1399</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0764</v>
+        <v>0.6502</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1803</v>
+        <v>0.6502</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2568</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5443</v>
+        <v>0.6502</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6167</v>
+        <v>0.6502</v>
       </c>
       <c r="L9" t="n">
-        <v>2.161</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5321</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4364</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0958</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5656</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.177</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0573</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1197</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8381</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBAÑEZ</t>
+          <t>J. CARRERAS MUÑOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUÑOZ</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6502</v>
+        <v>0.2245</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6502</v>
+        <v>-0.1071</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.3316</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6502</v>
+        <v>-1.5458</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6502</v>
+        <v>-0.0779</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-1.4678</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6502</v>
+        <v>-2.3209</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6502</v>
+        <v>-1.1737</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.1472</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.7751</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.0958</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.3207</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.6738</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.9468</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.273</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3634</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.9035</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.034</v>
+        <v>0.1916</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5938</v>
+        <v>-1.4426</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5599</v>
+        <v>1.6342</v>
       </c>
       <c r="G12" t="n">
         <v>1.181</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2328</v>
+        <v>0.4583</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1818</v>
+        <v>0.333</v>
       </c>
       <c r="U12" t="n">
-        <v>0.051</v>
+        <v>0.1254</v>
       </c>
       <c r="V12" t="n">
         <v>0.9346</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1284</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5509</v>
+        <v>-1.3586</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4225</v>
+        <v>0.472</v>
       </c>
       <c r="G13" t="n">
         <v>-0.2452</v>
@@ -1468,13 +1468,13 @@
         <v>0.3665</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3335</v>
+        <v>-0.0916</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0369</v>
+        <v>0.1554</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2965</v>
+        <v>-0.247</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.6656</v>
+        <v>-3.0307</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.7925</v>
+        <v>-3.2566</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1268</v>
+        <v>0.2259</v>
       </c>
       <c r="G14" t="n">
         <v>-2.2837</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0154</v>
+        <v>-0.3805</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6244</v>
+        <v>-0.0886</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.391</v>
+        <v>-0.2919</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7992</v>
+        <v>11.3497</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4667</v>
+        <v>4.017099999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>7.332400000000001</v>
+        <v>7.332399999999999</v>
       </c>
       <c r="G15" t="n">
         <v>8.509</v>
@@ -1603,7 +1603,7 @@
         <v>8.212700000000002</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6381999999999999</v>
+        <v>-0.6381999999999997</v>
       </c>
       <c r="M15" t="n">
         <v>0.9345</v>
@@ -1615,7 +1615,7 @@
         <v>-5.932900000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9162000000000006</v>
+        <v>0.9161999999999997</v>
       </c>
       <c r="Q15" t="n">
         <v>-13.7443</v>
@@ -1624,16 +1624,16 @@
         <v>14.6606</v>
       </c>
       <c r="S15" t="n">
-        <v>0.46</v>
+        <v>1.0104</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2809</v>
+        <v>3.831300000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.8208</v>
+        <v>-2.8207</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9138999999999998</v>
+        <v>0.9138999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>6.355799999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0248</v>
+        <v>2.0816</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2977</v>
+        <v>2.2016</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2729</v>
+        <v>-0.12</v>
       </c>
       <c r="G16" t="n">
         <v>1.9351</v>
@@ -1702,13 +1702,13 @@
         <v>0.1833</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0936</v>
+        <v>-0.0368</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2557</v>
+        <v>0.1595</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3493</v>
+        <v>-0.1963</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. RAMON AÑIBARRO</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9502</v>
+        <v>1.1743</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9502</v>
+        <v>-0.2484</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.4227</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9502</v>
+        <v>-1.2419</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3251</v>
+        <v>-0.3537</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6251</v>
+        <v>-0.8882</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9502</v>
+        <v>-1.4078</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3251</v>
+        <v>-0.8085</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6251</v>
+        <v>-0.5994</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.1659</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.4548</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.2888</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>N. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8304</v>
+        <v>0.9502</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0401</v>
+        <v>0.9502</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7903</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2419</v>
+        <v>0.9502</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3537</v>
+        <v>0.3251</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8882</v>
+        <v>0.6251</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4078</v>
+        <v>0.9502</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8085</v>
+        <v>0.3251</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5994</v>
+        <v>0.6251</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1659</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4548</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2888</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1659</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4925</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6584</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4836</v>
+        <v>0.8973</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8608</v>
+        <v>1.2454</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3772</v>
+        <v>-0.3481</v>
       </c>
       <c r="G19" t="n">
         <v>1.4471</v>
@@ -1936,13 +1936,13 @@
         <v>2.0158</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2305</v>
+        <v>0.1833</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.1855</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3396</v>
+        <v>0.3688</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.471</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="E20" t="n">
         <v>-1.2093</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6803</v>
+        <v>2.0445</v>
       </c>
       <c r="G20" t="n">
         <v>0.0194</v>
@@ -2014,13 +2014,13 @@
         <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1164</v>
+        <v>0.2477</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0196</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0969</v>
+        <v>0.2673</v>
       </c>
       <c r="V20" t="n">
         <v>0.9346</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2152</v>
+        <v>0.7062</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3031</v>
+        <v>0.5916</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.1147</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0643</v>
@@ -2092,13 +2092,13 @@
         <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2257</v>
+        <v>0.2653</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0188</v>
+        <v>0.2696</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2069</v>
+        <v>-0.0043</v>
       </c>
       <c r="V21" t="n">
         <v>0.3219</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5546</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1528</v>
+        <v>0.2318</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4018</v>
+        <v>-0.3232</v>
       </c>
       <c r="G23" t="n">
         <v>-0.247</v>
@@ -2248,13 +2248,13 @@
         <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4908</v>
+        <v>-0.0275</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2202</v>
+        <v>0.1644</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2706</v>
+        <v>-0.1919</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4487</v>
+        <v>-0.3197</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7449</v>
+        <v>-1.9756</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2961</v>
+        <v>1.656</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0656</v>
@@ -2326,13 +2326,13 @@
         <v>2.3823</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8046</v>
+        <v>0.3245</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.589</v>
+        <v>0.1803</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2156</v>
+        <v>0.1442</v>
       </c>
       <c r="V24" t="n">
         <v>0.9554</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>M. AROCA RUBIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.7766</v>
+        <v>-3.8735</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4774</v>
+        <v>-3.776</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2992</v>
+        <v>-0.0975</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.6444</v>
+        <v>-0.6247</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.2272</v>
+        <v>-1.051</v>
       </c>
       <c r="I25" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.7925</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="M25" t="n">
         <v>-1.4172</v>
       </c>
-      <c r="J25" t="n">
-        <v>-2.1223</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-2.3723</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-2.5222</v>
-      </c>
       <c r="N25" t="n">
-        <v>-0.8549</v>
+        <v>-1.032</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.6673</v>
+        <v>-0.3852</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3665</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8326</v>
+        <v>-4.5814</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1991</v>
+        <v>2.7489</v>
       </c>
       <c r="S25" t="n">
-        <v>3.7683</v>
+        <v>-0.1701</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4774</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2908</v>
+        <v>-0.1622</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.267</v>
+        <v>-1.2461</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="X25" t="n">
         <v>-1.267</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.9935</v>
+        <v>-4.1529</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.9816</v>
+        <v>-2.689</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.0119</v>
+        <v>-1.464</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.9728</v>
+        <v>-4.6444</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.444</v>
+        <v>-3.2272</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4711</v>
+        <v>-1.4172</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.3788</v>
+        <v>-2.1223</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.0811</v>
+        <v>-2.3723</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.2978</v>
+        <v>0.25</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.594</v>
+        <v>-2.5222</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.3629</v>
+        <v>-0.8549</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7689</v>
+        <v>-1.6673</v>
       </c>
       <c r="P26" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-1.8326</v>
       </c>
-      <c r="Q26" t="n">
-        <v>-3.6651</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.8326</v>
+        <v>2.1991</v>
       </c>
       <c r="S26" t="n">
-        <v>0.38</v>
+        <v>1.392</v>
       </c>
       <c r="T26" t="n">
-        <v>1.4631</v>
+        <v>1.2659</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0831</v>
+        <v>0.1261</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.5681</v>
+        <v>-1.267</v>
       </c>
       <c r="W26" t="n">
-        <v>1.5993</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.1674</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M. AROCA RUBIO</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.0559</v>
+        <v>-5.8565</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.2183</v>
+        <v>-2.6547</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8376</v>
+        <v>-3.2018</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6247</v>
+        <v>-2.9728</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.051</v>
+        <v>-3.444</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4263</v>
+        <v>0.4711</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7925</v>
+        <v>-1.3788</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.019</v>
+        <v>-1.0811</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8115</v>
+        <v>-0.2978</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.4172</v>
+        <v>-1.594</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.032</v>
+        <v>-2.3629</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.3852</v>
+        <v>0.7689</v>
       </c>
       <c r="P27" t="n">
         <v>-1.8326</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.5814</v>
+        <v>-3.6651</v>
       </c>
       <c r="R27" t="n">
-        <v>2.7489</v>
+        <v>1.8326</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.3525</v>
+        <v>0.517</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.4502</v>
+        <v>0.79</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.9023</v>
+        <v>-0.273</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.2461</v>
+        <v>-1.5681</v>
       </c>
       <c r="W27" t="n">
-        <v>0.0208</v>
+        <v>1.5993</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.267</v>
+        <v>-3.1674</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-10.799</v>
+        <v>-7.593999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.332400000000001</v>
+        <v>-7.3324</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.4667</v>
+        <v>-0.2615999999999996</v>
       </c>
       <c r="G28" t="n">
         <v>-8.508900000000001</v>
@@ -2623,13 +2623,13 @@
         <v>-7.574700000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>-8.2126</v>
+        <v>-8.212599999999998</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6378999999999999</v>
+        <v>0.6379</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.9161000000000001</v>
+        <v>-0.9160999999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>-14.6606</v>
@@ -2638,19 +2638,19 @@
         <v>13.7445</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.4599000000000002</v>
+        <v>2.7452</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8208</v>
+        <v>2.8207</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.2809</v>
+        <v>-0.07550000000000007</v>
       </c>
       <c r="V28" t="n">
         <v>-0.9138999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>5.4417</v>
+        <v>5.441699999999999</v>
       </c>
       <c r="X28" t="n">
         <v>-6.355700000000001</v>
